--- a/sample_data/sample_output/TAM0318F.xlsx
+++ b/sample_data/sample_output/TAM0318F.xlsx
@@ -18,9 +18,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
-    <numFmt numFmtId="165" formatCode="$#,##0.00"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
+    <numFmt numFmtId="166" formatCode="$#,##0.00"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -61,10 +62,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -717,7 +718,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -2190,10 +2191,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B2" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C2" s="4" t="n">
         <v>1</v>
@@ -2570,10 +2569,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B3" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C3" s="4" t="n">
         <v>1</v>
@@ -2950,10 +2947,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B4" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>1</v>
@@ -3452,10 +3447,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>1</v>
@@ -3950,10 +3943,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B6" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>1</v>
@@ -4440,10 +4431,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>1</v>
@@ -4946,10 +4935,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>1</v>
@@ -5440,10 +5427,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>1</v>
@@ -5938,10 +5923,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>1</v>
@@ -6420,10 +6403,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B11" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>2</v>
@@ -6802,10 +6783,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>2</v>
@@ -7332,10 +7311,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>2</v>
@@ -7856,10 +7833,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>2</v>
@@ -8346,10 +8321,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>2</v>
@@ -8844,10 +8817,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>2</v>
@@ -9344,10 +9315,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>2</v>
@@ -9844,10 +9813,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B18" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>3</v>
@@ -10372,10 +10339,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B19" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>3</v>
@@ -10900,10 +10865,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>3</v>
@@ -11424,10 +11387,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>3</v>
@@ -11942,10 +11903,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>3</v>
@@ -12486,10 +12445,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B23" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>3</v>
@@ -13012,10 +12969,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B24" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>3</v>
@@ -13540,10 +13495,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B25" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>3</v>
@@ -14056,10 +14009,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B26" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>4</v>
@@ -14582,10 +14533,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>4</v>
@@ -15114,10 +15063,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B28" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>4</v>
@@ -15640,10 +15587,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B29" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>4</v>
@@ -16168,10 +16113,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B30" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>4</v>
@@ -16696,10 +16639,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B31" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>4</v>
@@ -17224,10 +17165,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B32" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>4</v>
@@ -17752,10 +17691,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B33" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>4</v>
@@ -18280,10 +18217,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B34" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>5</v>
@@ -18736,10 +18671,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B35" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>5</v>
@@ -19192,10 +19125,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B36" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C36" s="4" t="n">
         <v>5</v>
@@ -19648,10 +19579,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B37" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C37" s="4" t="n">
         <v>5</v>
@@ -20224,10 +20153,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B38" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C38" s="4" t="n">
         <v>5</v>
@@ -20810,10 +20737,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B39" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C39" s="4" t="n">
         <v>5</v>
@@ -21384,10 +21309,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B40" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C40" s="4" t="n">
         <v>5</v>
@@ -21958,10 +21881,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B41" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C41" s="4" t="n">
         <v>5</v>
@@ -22536,10 +22457,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B42" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C42" s="4" t="n">
         <v>5</v>
@@ -23110,10 +23029,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B43" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C43" s="4" t="n">
         <v>5</v>
@@ -23684,10 +23601,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B44" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C44" s="4" t="n">
         <v>6</v>
@@ -24102,10 +24017,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B45" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C45" s="4" t="n">
         <v>6</v>
@@ -24520,10 +24433,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B46" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C46" s="4" t="n">
         <v>6</v>
@@ -25058,10 +24969,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B47" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C47" s="4" t="n">
         <v>6</v>
@@ -25594,10 +25503,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B48" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C48" s="4" t="n">
         <v>6</v>
@@ -26128,10 +26035,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B49" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C49" s="4" t="n">
         <v>6</v>
@@ -26660,10 +26565,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B50" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C50" s="4" t="n">
         <v>6</v>
@@ -27188,10 +27091,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B51" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C51" s="4" t="n">
         <v>6</v>
@@ -27740,10 +27641,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B52" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C52" s="4" t="n">
         <v>7</v>
@@ -28166,10 +28065,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B53" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C53" s="4" t="n">
         <v>7</v>
@@ -28592,10 +28489,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B54" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C54" s="4" t="n">
         <v>7</v>
@@ -29150,10 +29045,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B55" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C55" s="4" t="n">
         <v>7</v>
@@ -29694,10 +29587,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B56" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B56" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C56" s="4" t="n">
         <v>7</v>
@@ -30240,10 +30131,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B57" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C57" s="4" t="n">
         <v>7</v>
@@ -30780,10 +30669,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B58" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C58" s="4" t="n">
         <v>7</v>
@@ -31328,10 +31215,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B59" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C59" s="4" t="n">
         <v>7</v>
@@ -31868,10 +31753,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B60" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C60" s="4" t="n">
         <v>7</v>
@@ -32416,10 +32299,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B61" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C61" s="4" t="n">
         <v>7</v>
@@ -32964,10 +32845,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B62" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B62" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C62" s="4" t="n">
         <v>7</v>
@@ -33504,10 +33383,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B63" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C63" s="4" t="n">
         <v>7</v>
@@ -34048,10 +33925,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B64" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C64" s="4" t="n">
         <v>7</v>
@@ -34592,10 +34467,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B65" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B65" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C65" s="4" t="n">
         <v>7</v>
@@ -35144,10 +35017,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B66" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C66" s="4" t="n">
         <v>8</v>
@@ -35560,10 +35431,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B67" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C67" s="4" t="n">
         <v>8</v>
@@ -35976,10 +35845,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B68" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C68" s="4" t="n">
         <v>8</v>
@@ -36516,10 +36383,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B69" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B69" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C69" s="4" t="n">
         <v>8</v>
@@ -37034,10 +36899,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B70" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B70" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C70" s="4" t="n">
         <v>8</v>
@@ -37570,10 +37433,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B71" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B71" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C71" s="4" t="n">
         <v>8</v>
@@ -38108,10 +37969,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B72" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B72" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C72" s="4" t="n">
         <v>8</v>
@@ -38646,10 +38505,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B73" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B73" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C73" s="4" t="n">
         <v>8</v>
@@ -39172,10 +39029,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B74" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B74" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C74" s="4" t="n">
         <v>8</v>
@@ -39698,10 +39553,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B75" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B75" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C75" s="4" t="n">
         <v>8</v>
@@ -40228,10 +40081,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B76" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B76" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C76" s="4" t="n">
         <v>8</v>
@@ -40758,10 +40609,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B77" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B77" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C77" s="4" t="n">
         <v>8</v>
@@ -41288,10 +41137,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B78" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B78" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C78" s="4" t="n">
         <v>8</v>
@@ -41818,10 +41665,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B79" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B79" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C79" s="4" t="n">
         <v>8</v>
@@ -42340,10 +42185,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B80" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B80" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C80" s="4" t="n">
         <v>9</v>
@@ -42808,10 +42651,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B81" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B81" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C81" s="4" t="n">
         <v>9</v>
@@ -43276,10 +43117,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B82" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B82" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C82" s="4" t="n">
         <v>9</v>
@@ -43744,10 +43583,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B83" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B83" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C83" s="4" t="n">
         <v>9</v>
@@ -44212,10 +44049,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B84" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B84" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C84" s="4" t="n">
         <v>9</v>
@@ -44680,10 +44515,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B85" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B85" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C85" s="4" t="n">
         <v>9</v>
@@ -45284,10 +45117,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B86" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B86" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C86" s="4" t="n">
         <v>9</v>
@@ -45882,10 +45713,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B87" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B87" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C87" s="4" t="n">
         <v>9</v>
@@ -46474,10 +46303,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B88" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B88" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C88" s="4" t="n">
         <v>9</v>
@@ -47060,10 +46887,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B89" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B89" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C89" s="4" t="n">
         <v>9</v>
@@ -47650,10 +47475,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B90" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B90" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C90" s="4" t="n">
         <v>9</v>
@@ -48240,10 +48063,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B91" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B91" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C91" s="4" t="n">
         <v>9</v>
@@ -48830,10 +48651,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B92" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B92" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C92" s="4" t="n">
         <v>9</v>
@@ -49416,10 +49235,8 @@
           <t>TAM</t>
         </is>
       </c>
-      <c r="B93" s="3" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
-        </is>
+      <c r="B93" s="3" t="n">
+        <v>46099</v>
       </c>
       <c r="C93" s="4" t="n">
         <v>9</v>
